--- a/config/random_tower/event.xlsx
+++ b/config/random_tower/event.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>精緻な彫像</t>
+          <t>精致的雕像</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>精巧な彫像が地面に倒れ、内側から金色の光がちらついている。</t>
+          <t>精致的雕像倒在地上，内侧闪着金色的光。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>彫像を立てる</t>
+          <t>立雕像</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="V6" s="1" t="inlineStr">
         <is>
-          <t>彫像の祝福を獲得し、仲間のHPが完全回復する。</t>
+          <t>获得雕像的祝福，伙伴的HP完全恢复。</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>叩き壊す</t>
+          <t>砸碎</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AG6" s="1" t="inlineStr">
         <is>
-          <t>金貨を獲得するが、呪われて仲間のHPが20%減少する。</t>
+          <t>获得金币，但受到诅咒，伙伴的生命值减少20%。</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AM6" s="1" t="inlineStr">
         <is>
-          <t>無視する</t>
+          <t>无视</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>何も起こらない</t>
+          <t>什么都不会发生</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>奇妙な彫像</t>
+          <t>奇怪的雕像</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>不思議な彫像が地面に倒れており、内側から眩い光が輝いている。</t>
+          <t>不可思议的雕像倒在地上，内侧发出耀眼的光芒。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>彫像を立てる</t>
+          <t>立雕像</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="V7" s="1" t="inlineStr">
         <is>
-          <t>彫像の祝福を獲得し、仲間の覚醒値が完全回復する。</t>
+          <t>获得雕像的祝福，伙伴的觉醒值完全恢复。</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>叩き壊す</t>
+          <t>砸碎</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="AG7" s="1" t="inlineStr">
         <is>
-          <t>金貨を獲得するが、呪われて仲間の覚醒値がリセットされる。</t>
+          <t>获得金币，但受到诅咒，伙伴的觉醒值被重置。</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AM7" s="1" t="inlineStr">
         <is>
-          <t>無視する</t>
+          <t>无视</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AR7" s="1" t="inlineStr">
         <is>
-          <t>彫像から微かな光が放たれ、降り注いだ。どうやら祝福を受けたようだ。次回の戦闘で、仲間が敵を戦闘不能にするたび攻撃力バフが100%上昇する(2ターン持続)。</t>
+          <t>雕像放出微光，倾泻而下。看来是收到了祝福。下次战斗中，伙伴使敌人无法战斗时，攻击力增益值上升100%（持续2回合）。</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>妨害スパイ</t>
+          <t>妨碍间谍</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>うっかりして、寝ていたスパイを起こしてしまった。</t>
+          <t>不小心吵醒了正在睡觉的间谍。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>慰める</t>
+          <t>安慰</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="V8" s="1" t="inlineStr">
         <is>
-          <t>寝ているスパイの後ろには宝箱があるようだ。</t>
+          <t>睡觉的间谍背后似乎有一个宝箱。</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>隠す</t>
+          <t>隐藏</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AG8" s="1" t="inlineStr">
         <is>
-          <t>スパイが怒りを爆発さ！ スパイの怒りにより、物理攻撃力と特殊攻撃力が10%減少する。さらに、編成中の仲間の覚醒値が減少します。</t>
+          <t>间谍愤怒爆发！由于间谍的愤怒，物理攻击力和特殊攻击力减少10%。另外，编成中的伙伴的觉醒值也会减少。</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>秘密の罠</t>
+          <t>秘密陷阱</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>ここは空っぽだが、微かに何かの音が聞こえる。</t>
+          <t>这里是空的，但可以隐约听到什么声音。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>聞き耳を立てる</t>
+          <t>竖起耳朵听</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="V9" s="1" t="inlineStr">
         <is>
-          <t>仲間歌声が聞こえた。次の戦闘開始時、味方の中で最初に攻撃する仲間が2倍ダメージを与える。</t>
+          <t>听到伙伴的歌声。下次战斗开始时，我方中最先攻击的伙伴造成2倍伤害。</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>探す</t>
+          <t>寻找</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AG9" s="1" t="inlineStr">
         <is>
-          <t>中に何か入っている宝箱を見つけた。</t>
+          <t>找到了里面装着什么东西的宝箱。</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>謎の宝箱</t>
+          <t>神秘宝箱</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>謎の宝箱を発見した。</t>
+          <t>发现了一个神秘的宝箱。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>石を投げる</t>
+          <t>扔石头</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="V10" s="1" t="inlineStr">
         <is>
-          <t>ミミックが石を飲み込んだが、歯を痛めたらしく、金貨入りの袋を落とした。</t>
+          <t>米米克吞下了一块石头，但似乎伤到了牙齿，把装有金币的袋子掉了下来。</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>調べる</t>
+          <t>调查</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AG10" s="1" t="inlineStr">
         <is>
-          <t>ミミックだった！仲間のHPが減少した。</t>
+          <t>是米米克！伙伴的HP减少了。</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="AM10" s="1" t="inlineStr">
         <is>
-          <t>慎重に進む</t>
+          <t>慎重地前进</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>宝箱を獲得した</t>
+          <t>获得宝箱</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>謎の宝箱</t>
+          <t>神秘宝箱</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>謎の宝箱を発見した。</t>
+          <t>发现了一个神秘的宝箱。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>石を投げる</t>
+          <t>扔石头</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="V11" s="1" t="inlineStr">
         <is>
-          <t>ミミックが石を飲み込んだが、歯を痛めたらしく、金貨入りの袋を落とした。</t>
+          <t>米米克吞下了一块石头，但似乎伤到了牙齿，把装有金币的袋子掉了下来。</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB11" s="1" t="inlineStr">
         <is>
-          <t>調べる</t>
+          <t>调查</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AG11" s="1" t="inlineStr">
         <is>
-          <t>宝箱を獲得した。</t>
+          <t>赢得了宝箱。</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AM11" s="1" t="inlineStr">
         <is>
-          <t>慎重に進む</t>
+          <t>慎重地前进</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>ミミックだった！編成パートナーのHPが減少した</t>
+          <t>是米米克！组织合作伙伴HP减少</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>怪しい3人組を発見した。</t>
+          <t>发现了三个可疑的人。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>挨拶する</t>
+          <t>打招呼</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="V12" s="1" t="inlineStr">
         <is>
-          <t>3人組は驚き、戦闘が開始した。仲間のHPが10%減少したが、覚醒値は上昇した。</t>
+          <t>三人大吃一惊，战斗开始了。伙伴的HP减少了10%，但是觉醒值上升了。</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB12" s="1" t="inlineStr">
         <is>
-          <t>観察する</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AG12" s="1" t="inlineStr">
         <is>
-          <t>彼らは金目のものを盗り、去った。後を追いかけ、遺された金貨+15000を見つけた。</t>
+          <t>他们偷了值钱的东西，就走了。追了上去，发现了遗留下来的+15000金币。</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>怪しい3人組を発見した。</t>
+          <t>发现了三个可疑的人。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>挨拶する</t>
+          <t>打招呼</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="V13" s="1" t="inlineStr">
         <is>
-          <t>3人組は驚き、逃げ出したが、慌てた拍子に金貨を落としていった。</t>
+          <t>三个人吓了一跳，逃跑了，慌慌张张的金币掉了下来。</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="AB13" s="1" t="inlineStr">
         <is>
-          <t>観察する</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="AG13" s="1" t="inlineStr">
         <is>
-          <t>彼らに発見され、対戦することになった。編成キャラのHPが10%減少したが、覚醒値は上昇した。</t>
+          <t>被他们发现，开始对战。编成角色的HP减少了10%，但是觉醒值上升了。</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>謎の人物</t>
+          <t>神秘人物</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>怪しい人物があなたに話しかけてきた。</t>
+          <t>有个可疑的人跟你说话了。</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>あなたは誰？</t>
+          <t>你是谁？</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="V14" s="1" t="inlineStr">
         <is>
-          <t>謎の人物は探検家と正体を明かした。ポケットから宝石を取り出し、宝石の祝福を得た。次の戦闘開始時、味方の仲間は初期覚醒値を1000獲得する。</t>
+          <t>神秘人物揭示了探险家和真实身份。从口袋里拿出宝石，得到宝石的祝福。下次战斗开始时，我方的伙伴获得初始觉醒值1000。</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AB14" s="1" t="inlineStr">
         <is>
-          <t>あなたはどこから来たのか</t>
+          <t>你从哪里来？</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AG14" s="1" t="inlineStr">
         <is>
-          <t>謎の人物がある方向を指差した。その方向を辿っていくと、不思議な装置を発見した。装置を起動し、200Ptを獲得！</t>
+          <t>神秘人物指向某个方向。顺着那个方向走，发现了不可思议的装置。启动设备并获得200pt ！</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AM14" s="1" t="inlineStr">
         <is>
-          <t>どこに行くの？</t>
+          <t>你要去哪里？</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="AR14" s="1" t="inlineStr">
         <is>
-          <t>神秘な人物は何も言わず、ポケットから袋を取り出して渡してきた(報酬を獲得)。</t>
+          <t>神秘人物什么也没说，从口袋里拿出一个袋子递给他（获得报酬）。</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>未知の力</t>
+          <t>未知的力量</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>何か奇妙な力が進行を妨げられているようだ。</t>
+          <t>好像有什么奇妙的力量阻碍着前进。</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>原因調査</t>
+          <t>原因调查</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="V15" s="1" t="inlineStr">
         <is>
-          <t>妨害装置を停止させ、報酬を獲得した。</t>
+          <t>停止干扰装置并获得报酬。</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="AB15" s="1" t="inlineStr">
         <is>
-          <t>回り道する</t>
+          <t>绕远路</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AG15" s="1" t="inlineStr">
         <is>
-          <t>新しい道を見つけ、何事もなく前に進む（何も起こらない）</t>
+          <t>找到一条新的道路，若无其事地前进（什么都没有发生）</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="AM15" s="1" t="inlineStr">
         <is>
-          <t>前へ進む</t>
+          <t>向前走</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AR15" s="1" t="inlineStr">
         <is>
-          <t>何かの仕掛けが作動したようだ。仲間の現在のHPが20%減少し、覚醒値が50%上昇した。</t>
+          <t>好像有什么机关启动了。伙伴的当前生命值减少20%，觉醒值上升50%。</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>七夜の願い</t>
+          <t>七夜的愿望</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>ご機嫌なスパイに遭遇した。あなたの願いを聞こうとしている。</t>
+          <t>遇到了心情愉快的间谍。我想听听你的愿望。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>強化する</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="V16" s="1" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、15%の確率で敵の現在のHPを半分まで減少する。この戦闘に初挑戦時のみ発動できる(以降発動不可)。</t>
+          <t>下次战斗开始时，有15%的机率将敌人当前生命值减少一半。此战斗只有初次挑战时才能发动（以后不可发动）。</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="AB16" s="1" t="inlineStr">
         <is>
-          <t>ダイヤが欲しい</t>
+          <t>我想要钻石</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AG16" s="1" t="inlineStr">
         <is>
-          <t>50ダイヤを獲得</t>
+          <t>赢得50颗钻石</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AM16" s="1" t="inlineStr">
         <is>
-          <t>金貨が欲しい</t>
+          <t>我想要金币</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AR16" s="1" t="inlineStr">
         <is>
-          <t>大量の金貨を獲得した。</t>
+          <t>获得了大量金币。</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>七夜の願い？</t>
+          <t>七夜的愿望？</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>無表情なスパイに遭遇した。あなたの願いを聞こうとしている。</t>
+          <t>遇到了面无表情的间谍。我想听听你的愿望。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>強化する</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="V17" s="1" t="inlineStr">
         <is>
-          <t>何も起こらなかった……いや。少量の金貨が残されているようだ。</t>
+          <t>什么都没有发生……不。似乎还剩下少量金币。</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>ダイヤが欲しい</t>
+          <t>我想要钻石</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AG17" s="1" t="inlineStr">
         <is>
-          <t>何も起きない………いや、そうではないようだ、ダイヤが少し残っていた。</t>
+          <t>什么都没发生……不，好像不是这样，钻石还残留着一点。</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="AM17" s="1" t="inlineStr">
         <is>
-          <t>金貨が欲しい</t>
+          <t>我想要金币</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>何も起こらない………いや、そうではないようだ、少し金貨が残っている</t>
+          <t>什么都没有发生……不，似乎不是，还剩下一些金币</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>七夜の願い？</t>
+          <t>七夜的愿望？</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>機嫌が悪いスパイに遭遇した。あなたの願いを聞こうとしている。</t>
+          <t>遇到了心情不好的间谍。我想听听你的愿望。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>強化する</t>
+          <t>强化</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="V18" s="1" t="inlineStr">
         <is>
-          <t>何も起こらなかった……いや。少量の金貨が残されているようだ。</t>
+          <t>什么都没有发生……不。似乎还剩下少量金币。</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AB18" s="1" t="inlineStr">
         <is>
-          <t>ダイヤが欲しい</t>
+          <t>我想要钻石</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AG18" s="1" t="inlineStr">
         <is>
-          <t>何も起きない………いや、そうではないようだ、ダイヤが少し残っていた。</t>
+          <t>什么都没发生……不，好像不是这样，钻石还残留着一点。</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AM18" s="1" t="inlineStr">
         <is>
-          <t>金貨が欲しい</t>
+          <t>我想要金币</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>何も起こらない………いや、そうではないようだ、少し金貨が残っている</t>
+          <t>什么都没有发生……不，似乎不是，还剩下一些金币</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>妨害スパイ</t>
+          <t>妨碍间谍</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>行く手を阻むスパイがぐっすりと寝ている。</t>
+          <t>阻挡去路的间谍正在酣睡。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>起こす</t>
+          <t>叫醒</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="V19" s="1" t="inlineStr">
         <is>
-          <t>スパイは拗ねて離れてしまった。</t>
+          <t>间谍闹别扭地离开了。</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AB19" s="1" t="inlineStr">
         <is>
-          <t>叩き起こす</t>
+          <t>敲醒</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AG19" s="1" t="inlineStr">
         <is>
-          <t>スパイが反撃してきた。反撃の影響で、仲間全員の攻撃力バフが5%減少した。</t>
+          <t>间谍反击了。由于反击的影响，全体伙伴的攻击力增益减少5%。</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>妨害スパイ</t>
+          <t>妨碍间谍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>行く手を阻むスパイがぐっすりと寝ている。</t>
+          <t>阻挡去路的间谍正在酣睡。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>起こす</t>
+          <t>叫醒</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="V20" s="1" t="inlineStr">
         <is>
-          <t>スパイが眠りから目覚め、キスをした。祝福―次の戦闘開始時、敵全員に沈黙を付与する(1ターン持続)。」</t>
+          <t>间谍从睡梦中醒来，吻了她。祝福—在下一场战斗开始时给所有敌人施加沉默（持续1回合）。”</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="AB20" s="1" t="inlineStr">
         <is>
-          <t>叩き起こす</t>
+          <t>敲醒</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AG20" s="1" t="inlineStr">
         <is>
-          <t>スパイが何かを持って走り去っていった。</t>
+          <t>间谍拿着什么东西跑开了。</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>困っている人</t>
+          <t>有困难的人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>困っている人物と遭遇した。アイスを買うからお金が欲しいとお願いされた。</t>
+          <t>遇到了有麻烦的人。因为买冰淇淋所以拜托我要钱。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>お金を渡す</t>
+          <t>给钱</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="V21" s="1" t="inlineStr">
         <is>
-          <t>彼は喜んで受け取り、代わりに不思議な石をくれた。次の戦闘開始時、全ての敵に睡眠状態を付与する(1ターン持続)。</t>
+          <t>他高兴地收下了，并给了我一块不可思议的石头。下次战斗开始时，给予全部敌人睡眠状态（持续1回合）。</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="AB21" s="1" t="inlineStr">
         <is>
-          <t>遠まわしに断る</t>
+          <t>委婉地拒绝</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="AG21" s="1" t="inlineStr">
         <is>
-          <t>がっかりした様子で去って行った。</t>
+          <t>失望地走了。</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AM21" s="1" t="inlineStr">
         <is>
-          <t>追い返す</t>
+          <t>赶走</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AR21" s="1" t="inlineStr">
         <is>
-          <t>彼の手にある神器が光を放ち、仲間たちは驚いてしまい、覚醒値が全てリセットされた。</t>
+          <t>他手中的神器发出光芒，伙伴们都吓了一跳，觉醒值全部重置。</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>平穏な日常？</t>
+          <t>平静的日常？</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>地面に財布が落ちていた。</t>
+          <t>钱包掉在地上。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>落とし主を待つ</t>
+          <t>等待失主</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="V22" s="1" t="inlineStr">
         <is>
-          <t>落とし主がやってきて、感謝された。あなたに金貨を渡した。</t>
+          <t>失主来了，很感谢。我给了你金币。</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AB22" s="1" t="inlineStr">
         <is>
-          <t>受け取る</t>
+          <t>收到</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="AG22" s="1" t="inlineStr">
         <is>
-          <t>金貨を獲得したが、罪悪感に押しつぶされ、味方の覚醒値がリセットされた。</t>
+          <t>虽然获得了金币，但被罪恶感压垮了，友方的觉醒值被重置了。</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AM22" s="1" t="inlineStr">
         <is>
-          <t>無視する</t>
+          <t>无视</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>何も起こらない</t>
+          <t>什么都不会发生</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>スパイの歌</t>
+          <t>间谍之歌</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>スパイが歌を歌おうとしている。</t>
+          <t>间谍要唱歌了。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>歌を聞く</t>
+          <t>听歌</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="V23" s="1" t="inlineStr">
         <is>
-          <t>穏やかに眠り、十分な睡眠を取った。仲間のHPが20%回復した。</t>
+          <t>平静地睡觉，充足的睡眠。伙伴的HP恢复了20%。</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="AB23" s="1" t="inlineStr">
         <is>
-          <t>制止する</t>
+          <t>制止</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="AG23" s="1" t="inlineStr">
         <is>
-          <t>スパイが激怒！連続ビンタを浴びせ、仲間のHPが減少した。しかし、覚醒値を獲得した。</t>
+          <t>间谍愤怒了！连续打，伙伴的HP减少了。但是获得了觉醒值。</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="AM23" s="1" t="inlineStr">
         <is>
-          <t>逃げる</t>
+          <t>逃跑</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AR23" s="1" t="inlineStr">
         <is>
-          <t>スパイの能力の影響範囲から逃れた。</t>
+          <t>脱离了间谍能力的影响范围。</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>スパイの歌</t>
+          <t>间谍之歌</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>スパイが歌を歌おうとしている。</t>
+          <t>间谍要唱歌了。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>歌を聞く</t>
+          <t>听歌</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="V24" s="1" t="inlineStr">
         <is>
-          <t>穏やかに眠り、十分な睡眠を取った。仲間のHPが20%回復した。</t>
+          <t>平静地睡觉，充足的睡眠。伙伴的HP恢复了20%。</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="AB24" s="1" t="inlineStr">
         <is>
-          <t>制止する</t>
+          <t>制止</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AG24" s="1" t="inlineStr">
         <is>
-          <t>スパイが激怒！連続ビンタを浴びせ、仲間のHPが減少した。しかし、覚醒値を獲得した。</t>
+          <t>间谍愤怒了！连续打，伙伴的HP减少了。但是获得了觉醒值。</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="AM24" s="1" t="inlineStr">
         <is>
-          <t>逃げる</t>
+          <t>逃跑</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="AR24" s="1" t="inlineStr">
         <is>
-          <t>しかし、逃げるのが遅すぎたためスパイの能力の影響を受けてしまった。仲間のHPが回復したが、覚醒値が減少した。</t>
+          <t>但是，由于逃跑太晚，受到了间谍能力的影响。伙伴的HP恢复了，但是觉醒值减少了。</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>自称神という人が現れ、袋を落としたか聞いてきた。</t>
+          <t>一个自称神的人出现了，问我袋子有没有掉。</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>金色の袋を落とした</t>
+          <t>金色的袋子掉了</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="V25" s="1" t="inlineStr">
         <is>
-          <t>大量の金貨を獲得したが、仲間のHPが減少した。</t>
+          <t>虽然获得了大量金币，但是伙伴的HP减少了。</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="AB25" s="1" t="inlineStr">
         <is>
-          <t>銀色の袋を落とした</t>
+          <t>银色的袋子掉了</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>大量の金貨を獲得したが、編成パートナーのHPが減少した</t>
+          <t>虽然获得了大量金币，但是编制伙伴的HP减少了</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AM25" s="1" t="inlineStr">
         <is>
-          <t>落とし物はない</t>
+          <t>没有失物</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="AR25" s="1" t="inlineStr">
         <is>
-          <t>正直な子供には報酬が与えられる。</t>
+          <t>诚实的孩子会得到奖励。</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -6021,14 +6021,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>愿望</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>願望</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>願望</t>
-        </is>
-      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Wish</t>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>あなたの願いを言いなさい。</t>
+          <t>说出你的愿望。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
+          <t>强攻</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>強攻</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>強攻</t>
-        </is>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>Strong attack</t>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="V26" s="1" t="inlineStr">
         <is>
-          <t>次の戦闘で、味方が敵を撃破すると攻撃力を100%上昇する(2ターン持続)。</t>
+          <t>在下一场战斗中，我方击破敌人时攻击力上升100%（持续2回合）。</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="AB26" s="1" t="inlineStr">
         <is>
+          <t>快速</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
           <t>高速</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>高速</t>
-        </is>
-      </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>Fast</t>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="AG26" s="1" t="inlineStr">
         <is>
-          <t>次回の戦闘開始時、仲間が初期覚醒値を1000獲得する。</t>
+          <t>下次战斗开始时，伙伴获得初始觉醒值1000。</t>
         </is>
       </c>
       <c r="AH26" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AM26" s="1" t="inlineStr">
         <is>
-          <t>棚からぼた餅</t>
+          <t>架子上的牡丹饼</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、敵は50%の確率で直接死亡する（各敵の確率単独で計算）</t>
+          <t>下次战斗开始时，敌人有50%的机率直接死亡（各敌人的机率单独计算）</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -6248,14 +6248,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>愿望</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>願望</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>願望</t>
-        </is>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Wish</t>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>あなたの願いを言いなさい。</t>
+          <t>说出你的愿望。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="V27" s="1" t="inlineStr">
         <is>
-          <t>味方戦闘不能時、すぐに復活し、HP50%と覚醒値100%を回復する(1回のみ発動)。</t>
+          <t>我方无法战斗时，会立刻复活，回复50%的生命值和100%的觉醒值（仅发动1次）。</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>強攻する</t>
+          <t>强攻</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、味方の最初に行動するパートナーが2倍ダメージを与える</t>
+          <t>下次战斗开始时，我方第一个行动的伙伴造成2倍伤害</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、全ての敵を1ターンの間沈黙させる</t>
+          <t>下一场战斗开始时，所有敌人沉默1回合。</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>食べる？やめとく？</t>
+          <t>吃吗？算了吧？</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>目の前にいる男性が肉を食べようとしている。</t>
+          <t>眼前的男子正准备吃肉。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>肉が食べたい</t>
+          <t>我想吃肉</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="V28" s="1" t="inlineStr">
         <is>
-          <t>仲間のHPが完全に回復する。</t>
+          <t>伙伴的HP完全恢复。</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>ネギが欲しい</t>
+          <t>我想要葱</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="AG28" s="1" t="inlineStr">
         <is>
-          <t>最終戦で、戦闘の第2ターンに敵全員の覚醒値を全てリセットする。</t>
+          <t>在最终战中，战斗的第2回合将所有敌人的觉醒值全部重置。</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AM28" s="1" t="inlineStr">
         <is>
-          <t>アヒルを助ける</t>
+          <t>帮助鸭子</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="AR28" s="1" t="inlineStr">
         <is>
-          <t>あの男と戦い、大きなアヒルを救い出した。仲間のHPが10%減少したが、大きなアヒルの加護を獲得。次の戦闘で最初にスキルを使用した際、会心率が30%上昇する。</t>
+          <t>和那个男人战斗，救出了大鸭子。伙伴的HP减少了10%，但是获得了大鸭子的加护。在下一场战斗中首次使用技能时，暴击率上升30%。</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>闇市商人</t>
+          <t>黑市商人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>闇市商人を自称する人物が現れた。危機から救ってくれるようだ。</t>
+          <t>出现了一个自称黑市商人的人。好像把我们从危机中解救出来了。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>話を聞く</t>
+          <t>倾听</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="V29" s="1" t="inlineStr">
         <is>
-          <t>ポケットから宝珠を取り出した。次の戦闘でターンが終了するごとにHPが10未満の敵を戦闘不能にする。</t>
+          <t>从口袋里取出宝珠。在下一个战斗回合结束时，使HP不足10的敌人不能战斗。</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>無視する</t>
+          <t>无视</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AG29" s="1" t="inlineStr">
         <is>
-          <t>「顧客拡大のため、今回は特別に安くにしておきますね」次回の戦闘開始時、敵全員に沈黙状態を付与する(1ターン持続)。</t>
+          <t>“为了扩大顾客，这次会特别便宜”下次战斗开始时，给予全体敌人沉默状态（持续1回合）。</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AM29" s="1" t="inlineStr">
         <is>
-          <t>警戒する</t>
+          <t>提高警惕</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="AR29" s="1" t="inlineStr">
         <is>
-          <t>おやおや、私は全然信用されていないようですね。では、この神秘のルーンをお渡ししましょう。」神秘のルーンの力を手に入れた。以降の戦闘で敵を倒した際、その周囲の敵にも40%のダメージを与える。</t>
+          <t>哎呀哎呀，我好像完全不被信任呢。那么，这个神秘的符文就交给您吧。”得到了神秘符文的力量。在以后的战斗中打倒敌人时，对其周围的敌人也给予40%的伤害。</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>謎の人物</t>
+          <t>神秘人物</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>怪しい人物があなたに話しかけてきた。</t>
+          <t>有个可疑的人跟你说话了。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>あなたは誰？</t>
+          <t>你是谁？</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="V30" s="1" t="inlineStr">
         <is>
-          <t>謎の人物が自ら盗賊だと正体を明かした。ポケットから霊玉を取り出し、霊玉の祝福を得た。次の戦闘以降、敵の最大HPが10%減少する。</t>
+          <t>谜样的人物表明自己是盗贼。从口袋里拿出灵玉，得到灵玉的祝福。下次战斗后，敌人最大生命值减少10%。</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>あなたはどこから来たのか</t>
+          <t>你从哪里来？</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="AG30" s="1" t="inlineStr">
         <is>
-          <t>謎の人物がある方向を指差した。その方向を辿っていくと、不思議な装置を発見した。装置を起動し、200Ptを獲得！</t>
+          <t>神秘人物指向某个方向。顺着那个方向走，发现了不可思议的装置。启动设备并获得200pt ！</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="AM30" s="1" t="inlineStr">
         <is>
-          <t>どこに行くの？</t>
+          <t>你要去哪里？</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>神秘な人物は何も言わず、ポケットから袋を取り出して渡してきた(報酬を獲得)。</t>
+          <t>神秘人物什么也没说，从口袋里拿出一个袋子递给他（获得报酬）。</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>スパイの祝福</t>
+          <t>间谍的祝福</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>スパイが現れた。あなたの勝利を確信し、祝福している。</t>
+          <t>间谍出现了。相信你的胜利，并祝贺你。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>ダメージが足りない。強化しなければ。</t>
+          <t>伤害不够。必须加强。</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="V31" s="1" t="inlineStr">
         <is>
-          <t>ダメージ上昇の祝福を受けた。各ターンの終了時、攻撃力が最も高い仲間の攻撃力20%の確定ダメージを敵全員に与える。</t>
+          <t>受到了伤害上升的祝福。各回合结束时，给予全体敌人攻击力最高的伙伴攻击力20%的真实伤害。</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>仲間は簡単に撃破されるため、生存力を高める。</t>
+          <t>因为伙伴很容易被击破，所以提高生存力。</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="AG31" s="1" t="inlineStr">
         <is>
-          <t>防御の加護を授ける。戦闘開始時、味方全体にシールドを付与する。このシールドは味方全員が受けるダメージを吸収し、その吸収量は味方仲間の中で最も高いHPと同等。</t>
+          <t>给予防御加护。战斗开始时，给予我方全体护盾。这个护盾吸收我方全体人员受到的伤害，其吸收量与我方伙伴中最高的生命值同等。</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AM31" s="1" t="inlineStr">
         <is>
-          <t>敵が強すぎる</t>
+          <t>敌人太强了</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="AR31" s="1" t="inlineStr">
         <is>
-          <t>湮滅の加護を授ける。味方の仲間が必殺スキルを発動すると、目標の全バフを解除する。</t>
+          <t>赐与湮灭的保佑。我方伙伴发动必杀技能时，解除目标全部增益。</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>今日の夜ご飯</t>
+          <t>今天的晚饭</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>時空激戦の守護者に遭遇した。今日の夕食に悩んでいるようだ。</t>
+          <t>遇到了时空激战的守护者。好像在为今天的晚饭而烦恼。</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>おにぎりを勧める</t>
+          <t>推荐饭团</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="V32" s="1" t="inlineStr">
         <is>
-          <t>あなたの意見を聞き入れ、おにぎりを買い、そのうち1つを分けてくれた。</t>
+          <t>听了你的意见，买了饭团，分了一个给我。</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AB32" s="1" t="inlineStr">
         <is>
-          <t>時間がないから弁当は後で食べよう</t>
+          <t>没时间了便当以后再吃吧</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="AG32" s="1" t="inlineStr">
         <is>
-          <t>あなたの提案を受け入れ、コンビニで弁当を買い、一部をあなたに分けてくれた。</t>
+          <t>接受了你的提案，在便利店买了便当，把一部分分给了你。</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>潜入捜査？</t>
+          <t>卧底？</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>巡護員が行方不明になった仲間を探索するため、協力して欲しいよう</t>
+          <t>希望你们协助巡护员寻找失踪的伙伴</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>協力する</t>
+          <t>合作</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="V33" s="1" t="inlineStr">
         <is>
-          <t>部屋に入った直後に不意打ちを受けた。仲間の体力が10%減少したが、覚醒値が上昇した。</t>
+          <t>刚进房间就遭到了突袭。伙伴的体力减少了10%，但是觉醒值上升了。</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="AB33" s="1" t="inlineStr">
         <is>
-          <t>疑いの表情</t>
+          <t>怀疑的表情</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AG33" s="1" t="inlineStr">
         <is>
-          <t>「まさか見破られるとは思わなかった。先に失礼するよ。」あなたは嫌な気持ちになり、編成中の仲間の覚醒値が上昇した。</t>
+          <t>“真没想到会被识破。我先告辞了。”你变得讨厌，编成中的伙伴的觉醒值上升了。</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>潜入捜査</t>
+          <t>潜入搜查</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>巡護員が行方不明になった仲間を探索するため、協力して欲しいよう</t>
+          <t>希望你们协助巡护员寻找失踪的伙伴</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>協力する</t>
+          <t>合作</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="V34" s="1" t="inlineStr">
         <is>
-          <t>巡護員と共に盗賊団と戦闘になった。仲間の体力が10%減少したが、覚醒値が上昇した。</t>
+          <t>与巡护员一起与盗贼团战斗。伙伴的体力减少了10%，但是觉醒值上升了。</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="AB34" s="1" t="inlineStr">
         <is>
-          <t>疑いの表情</t>
+          <t>怀疑的表情</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AG34" s="1" t="inlineStr">
         <is>
-          <t>「信じてもらえないなら仕方ない。では、仲間を治癒しましょう。」編成中の仲間のHPが回復した。</t>
+          <t>“不相信的话也没办法。那么，治愈伙伴吧。”编成中的伙伴的HP恢复了。</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>お菓子の部屋</t>
+          <t>糖果的房间</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>お菓子作りの部屋に入ったが、どうやら誰もいないようだ。</t>
+          <t>进入制作点心的房间，但好像没有人。</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>つまみ食い</t>
+          <t>抓着吃</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="V35" s="1" t="inlineStr">
         <is>
-          <t>仲間のHPが回復した。</t>
+          <t>伙伴的HP恢复了。</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="AB35" s="1" t="inlineStr">
         <is>
-          <t>テイクアウトする</t>
+          <t>外带</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AG35" s="1" t="inlineStr">
         <is>
-          <t>もう少しで見つかりそうだった。逃げ足が速くてよかった。</t>
+          <t>差一点就找到了。幸好逃得快。</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>謎の人物</t>
+          <t>神秘人物</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>怪しい人物があなたに話しかけてきた。</t>
+          <t>有个可疑的人跟你说话了。</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>あなたは誰？</t>
+          <t>你是谁？</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="V37" s="1" t="inlineStr">
         <is>
-          <t>謎の人物は「ドンッ」という音を立て、一瞬で去った。</t>
+          <t>神秘人物“咚”的一声，瞬间离开了。</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="AB37" s="1" t="inlineStr">
         <is>
-          <t>あなたはどこから来たのか</t>
+          <t>你从哪里来？</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>謎の人物がある方向を指差した。その方向を辿っていくと、不思議な装置を発見した。装置を起動すると、中から時空Ptと金貨を獲得した。</t>
+          <t>神秘人物指向某个方向。顺着那个方向走，发现了不可思议的装置。启动装置后，从中获得时空Pt和金币。</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AM37" s="1" t="inlineStr">
         <is>
-          <t>どこに行くの？</t>
+          <t>你要去哪里？</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>謎の人物は何も言いたくなさそうだった。ポケットから袋を取り出し、あなたに渡した</t>
+          <t>神秘人物似乎什么都不想说。我从口袋里拿出一个袋子，递给你</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>謎の人物</t>
+          <t>神秘人物</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>怪しい人物があなたに話しかけてきた。</t>
+          <t>有个可疑的人跟你说话了。</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="Q38" s="1" t="inlineStr">
         <is>
-          <t>あなたは誰？</t>
+          <t>你是谁？</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="V38" s="1" t="inlineStr">
         <is>
-          <t>謎の人物がある方向を指差した。その方向に進むと、奇妙な装置を発見。装置を起動したら、50ポイントと金貨を手に入れた。</t>
+          <t>神秘人物指向某个方向。在那个方向前进，发现一个奇怪的设备。启动装置后，得到了50分和金币。</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AB38" s="1" t="inlineStr">
         <is>
-          <t>あなたはどこから来たのか</t>
+          <t>你从哪里来？</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="AG38" s="1" t="inlineStr">
         <is>
-          <t>謎の人物は何も言いたくなさそうだった。ポケットから袋を取り出し、渡してきた。</t>
+          <t>神秘人物似乎什么都不想说。他从口袋里拿出一个袋子递给我。</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="AM38" s="1" t="inlineStr">
         <is>
-          <t>どこに行くの？</t>
+          <t>你要去哪里？</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>謎の人物は「バン」と音を立てて、飛ぶように逃げていった</t>
+          <t>神秘人物“砰”的一声飞也似的逃走了</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>謎の人物</t>
+          <t>神秘人物</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>怪しい人物があなたに話しかけてきた。</t>
+          <t>有个可疑的人跟你说话了。</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>あなたは誰？</t>
+          <t>你是谁？</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="V39" s="1" t="inlineStr">
         <is>
-          <t>謎の人物がある方向を指差した。その方向に進むと、奇妙な装置を発見。装置を起動したら、50ポイントと金貨を手に入れた。</t>
+          <t>神秘人物指向某个方向。在那个方向前进，发现一个奇怪的设备。启动装置后，得到了50分和金币。</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="AB39" s="1" t="inlineStr">
         <is>
-          <t>あなたはどこから来たのか</t>
+          <t>你从哪里来？</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AG39" s="1" t="inlineStr">
         <is>
-          <t>謎の人物は何も言いたくなさそうだった。ポケットから袋を取り出し、渡してきた。</t>
+          <t>神秘人物似乎什么都不想说。他从口袋里拿出一个袋子递给我。</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AM39" s="1" t="inlineStr">
         <is>
-          <t>どこに行くの？</t>
+          <t>你要去哪里？</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="AR39" s="1" t="inlineStr">
         <is>
-          <t>謎の人物は考え込みながら、小さな袋を取り出し、渡してきた。</t>
+          <t>神秘人物一边沉思，一边拿出一个小袋子递了过来。</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
